--- a/models/test_data_IZ_to_IZ.xlsx
+++ b/models/test_data_IZ_to_IZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\iz_to_iz_transfer\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCE19EA-A9B0-488D-8AD7-CC97808A8A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8B217A-9589-4647-8416-B015B47E4C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="3390" windowWidth="21600" windowHeight="11265" tabRatio="800" activeTab="6" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="12645" tabRatio="800" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="156">
   <si>
     <t>Barcode</t>
   </si>
@@ -422,12 +422,6 @@
     <t>Request cancellation note</t>
   </si>
   <si>
-    <t>9973006592805504</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
     <t>When transfering loans, make only returns in source IZ</t>
   </si>
   <si>
@@ -477,6 +471,48 @@
   </si>
   <si>
     <t>OLD_UBS000034399</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>NB max treatments</t>
+  </si>
+  <si>
+    <t>Between 1 and 10'000</t>
+  </si>
+  <si>
+    <t>Add OLD_ prefix to items</t>
+  </si>
+  <si>
+    <t>Update the source items</t>
+  </si>
+  <si>
+    <t>Use MongoDB</t>
+  </si>
+  <si>
+    <t>DB name must be &lt;dest IZ&gt;_&lt;dest_lib&gt;</t>
+  </si>
+  <si>
+    <t>Used to create collection name in MongoDB</t>
+  </si>
+  <si>
+    <t>UBS000034398</t>
+  </si>
+  <si>
+    <t>UBS000034397</t>
+  </si>
+  <si>
+    <t>UBS000034396</t>
+  </si>
+  <si>
+    <t>9973125575405504</t>
+  </si>
+  <si>
+    <t>9973125573605504</t>
+  </si>
+  <si>
+    <t>9972994698105504</t>
   </si>
 </sst>
 </file>
@@ -901,7 +937,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -930,7 +966,7 @@
         <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
@@ -965,9 +1001,11 @@
       <c r="A9" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -983,7 +1021,7 @@
         <v>120</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
         <v>121</v>
@@ -994,7 +1032,7 @@
         <v>122</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
         <v>121</v>
@@ -1002,120 +1040,111 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>112</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" spans="1:4" ht="30">
-      <c r="A20" s="10" t="s">
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="3">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="30">
+      <c r="A23" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B23" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C23" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D23" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="45">
-      <c r="A21" t="s">
+    <row r="24" spans="1:4" ht="45">
+      <c r="A24" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="45.95" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="60">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30">
-      <c r="A24" t="s">
-        <v>66</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>79</v>
@@ -1124,73 +1153,122 @@
         <v>79</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="30">
-      <c r="A25" t="s">
-        <v>67</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="45.95" customHeight="1">
+      <c r="A25" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="30">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="60">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="30">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="30">
+      <c r="A28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30">
-      <c r="A29" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>72</v>
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30">
       <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="30">
+      <c r="A32" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="30">
+      <c r="A33" t="s">
         <v>116</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>117</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20" xr:uid="{C760ED61-BFB4-4FBF-9913-3DE2DE713A3F}">
+      <formula1>1</formula1>
+      <formula2>10000</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -1204,7 +1282,7 @@
           <x14:formula1>
             <xm:f>data_validation!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B12:B18</xm:sqref>
+          <xm:sqref>B13 B17:B19 B21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3BA26AD9-284C-4EA0-B5B0-2A9B21BCA870}">
           <x14:formula1>
@@ -1216,7 +1294,7 @@
           <x14:formula1>
             <xm:f>data_validation!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>B20:C26</xm:sqref>
+          <xm:sqref>B23:C29</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1501,7 +1579,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -1544,7 +1622,27 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1621,14 +1719,18 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="12" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="12"/>
+      <c r="A3" s="12" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="12"/>
+      <c r="A4" s="12" t="s">
+        <v>155</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1721,39 +1823,39 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
         <v>129</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>132</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>133</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>135</v>
-      </c>
-      <c r="H1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1771,10 +1873,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/models/test_data_IZ_to_IZ.xlsx
+++ b/models/test_data_IZ_to_IZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\iz_to_iz_transfer\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8B217A-9589-4647-8416-B015B47E4C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7611C47-C781-491E-AAF6-D81940B5D130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="12645" tabRatio="800" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="800" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -1105,7 +1105,7 @@
         <v>143</v>
       </c>
       <c r="B20" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>

--- a/models/test_data_IZ_to_IZ.xlsx
+++ b/models/test_data_IZ_to_IZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\iz_to_iz_transfer\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7611C47-C781-491E-AAF6-D81940B5D130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5E594A-B813-4F06-A155-D5A2F43723B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="800" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="800" activeTab="2" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="157">
   <si>
     <t>Barcode</t>
   </si>
@@ -513,6 +513,9 @@
   </si>
   <si>
     <t>9972994698105504</t>
+  </si>
+  <si>
+    <t>2227971445630005504</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1108,7 @@
         <v>143</v>
       </c>
       <c r="B20" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
@@ -1656,7 +1659,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -1693,6 +1696,14 @@
       </c>
       <c r="B4" s="8" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/models/test_data_IZ_to_IZ.xlsx
+++ b/models/test_data_IZ_to_IZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\iz_to_iz_transfer\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5E594A-B813-4F06-A155-D5A2F43723B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6568222-5C60-4480-81E5-2BC8EB4E24C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="800" activeTab="2" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" tabRatio="800" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -1108,7 +1108,7 @@
         <v>143</v>
       </c>
       <c r="B20" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>

--- a/models/test_data_IZ_to_IZ.xlsx
+++ b/models/test_data_IZ_to_IZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\iz_to_iz_transfer\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6568222-5C60-4480-81E5-2BC8EB4E24C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D34B40-42C8-497E-B2BB-2B920AB18F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" tabRatio="800" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
+    <workbookView xWindow="5235" yWindow="4740" windowWidth="21600" windowHeight="12645" tabRatio="800" activeTab="7" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,11 @@
     <sheet name="PoLines" sheetId="9" r:id="rId5"/>
     <sheet name="Loans" sheetId="10" r:id="rId6"/>
     <sheet name="Requests" sheetId="11" r:id="rId7"/>
-    <sheet name="Locations_mapping" sheetId="3" r:id="rId8"/>
-    <sheet name="Funds_mapping" sheetId="12" r:id="rId9"/>
-    <sheet name="Vendors_mapping" sheetId="7" r:id="rId10"/>
-    <sheet name="data_validation" sheetId="4" state="hidden" r:id="rId11"/>
+    <sheet name="Collections" sheetId="13" r:id="rId8"/>
+    <sheet name="Locations_mapping" sheetId="3" r:id="rId9"/>
+    <sheet name="Funds_mapping" sheetId="12" r:id="rId10"/>
+    <sheet name="Vendors_mapping" sheetId="7" r:id="rId11"/>
+    <sheet name="data_validation" sheetId="4" state="hidden" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="165">
   <si>
     <t>Barcode</t>
   </si>
@@ -516,6 +517,30 @@
   </si>
   <si>
     <t>2227971445630005504</t>
+  </si>
+  <si>
+    <t>Collection_id_s</t>
+  </si>
+  <si>
+    <t>Parent_col_id_s</t>
+  </si>
+  <si>
+    <t>Parent_col_id_d</t>
+  </si>
+  <si>
+    <t>Copy_bibs</t>
+  </si>
+  <si>
+    <t>81369750750005504</t>
+  </si>
+  <si>
+    <t>81369883050005504</t>
+  </si>
+  <si>
+    <t>81369883060005504</t>
+  </si>
+  <si>
+    <t>Collection_id_d</t>
   </si>
 </sst>
 </file>
@@ -1306,6 +1331,46 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99D418-FB11-4449-B88D-57A5CC883B32}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA927E34-BE12-40DF-B526-F644C6AE1FDF}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -1374,7 +1439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A0D6C5-D024-428E-995D-36256CF838C1}">
   <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
@@ -1896,6 +1961,68 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87848E35-8186-466E-ADBB-056867D1CB16}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="4" width="17.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CD200A-AAE3-41A8-B7B7-08FF5A82F532}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -1952,44 +2079,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99D418-FB11-4449-B88D-57A5CC883B32}">
-  <sheetPr>
-    <tabColor theme="9" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="25.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/models/test_data_IZ_to_IZ.xlsx
+++ b/models/test_data_IZ_to_IZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\iz_to_iz_transfer\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D34B40-42C8-497E-B2BB-2B920AB18F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7876D6C-D77A-44BA-9D60-662AD39BD618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="4740" windowWidth="21600" windowHeight="12645" tabRatio="800" activeTab="7" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="800" firstSheet="1" activeTab="4" xr2:uid="{AD365A3D-3304-46D8-98A5-452209B6D1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="165">
   <si>
     <t>Barcode</t>
   </si>
@@ -333,24 +333,6 @@
     <t>Physical Item Id</t>
   </si>
   <si>
-    <t>9972798270405504</t>
-  </si>
-  <si>
-    <t>22434853660005504</t>
-  </si>
-  <si>
-    <t>23454312290005504</t>
-  </si>
-  <si>
-    <t>23454312280005504</t>
-  </si>
-  <si>
-    <t>23443623250005504</t>
-  </si>
-  <si>
-    <t>POL-UBS-2025-167396</t>
-  </si>
-  <si>
     <t>Fundforall</t>
   </si>
   <si>
@@ -541,13 +523,31 @@
   </si>
   <si>
     <t>Collection_id_d</t>
+  </si>
+  <si>
+    <t>UBS-A100-17</t>
+  </si>
+  <si>
+    <t>A100-17</t>
+  </si>
+  <si>
+    <t>22487956980005504</t>
+  </si>
+  <si>
+    <t>23487956970005504</t>
+  </si>
+  <si>
+    <t>9919708540105504</t>
+  </si>
+  <si>
+    <t>POL-UBS-2026-214046</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,6 +595,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -619,12 +626,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -646,11 +654,13 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DAFBFA39-22AE-4E9D-AC20-8AE095ED5982}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{51B8D781-AE44-4138-B03D-1D28C37B98C1}"/>
+    <cellStyle name="Pourcentage" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -994,7 +1004,7 @@
         <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
@@ -1033,7 +1043,7 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1046,61 +1056,61 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>53</v>
@@ -1108,46 +1118,46 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1186,7 +1196,7 @@
     </row>
     <row r="25" spans="1:4" ht="45.95" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>78</v>
@@ -1270,7 +1280,7 @@
     </row>
     <row r="32" spans="1:4" ht="30">
       <c r="A32" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>72</v>
@@ -1278,13 +1288,13 @@
     </row>
     <row r="33" spans="1:4" ht="30">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1343,10 +1353,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1354,15 +1364,15 @@
         <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1375,7 +1385,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20.7109375" style="5" customWidth="1"/>
@@ -1383,16 +1393,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1402,8 +1412,6 @@
       <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
@@ -1413,24 +1421,38 @@
         <v>64</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1692,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1690,27 +1712,27 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1790,7 @@
         <v>62</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1795,17 +1817,17 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="12" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1840,45 +1862,24 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>95</v>
+        <v>164</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>98</v>
-      </c>
+      <c r="A3"/>
+      <c r="B3"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>99</v>
-      </c>
+      <c r="A4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1899,39 +1900,39 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" t="s">
         <v>127</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
         <v>128</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>129</v>
-      </c>
-      <c r="D1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1949,10 +1950,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1974,24 +1975,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>164</v>
-      </c>
       <c r="D1" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>52</v>
@@ -1999,10 +2000,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>52</v>
@@ -2010,7 +2011,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>53</v>
